--- a/Result/profitability/2221.xlsx
+++ b/Result/profitability/2221.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6024999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="N2" t="n">
-        <v>20.3375</v>
+        <v>20.7875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.50875</v>
+        <v>0.57</v>
       </c>
       <c r="N3" t="n">
-        <v>19.8075</v>
+        <v>20.205</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42625</v>
+        <v>0.49125</v>
       </c>
       <c r="N4" t="n">
-        <v>19.63375</v>
+        <v>20.1725</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0.30125</v>
+        <v>0.38625</v>
       </c>
       <c r="N5" t="n">
-        <v>18.17375</v>
+        <v>18.3925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1725</v>
+        <v>0.2475</v>
       </c>
       <c r="N6" t="n">
-        <v>16.33625</v>
+        <v>16.99125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.53</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03499999999999999</v>
+        <v>0.1075</v>
       </c>
       <c r="N7" t="n">
-        <v>13.57125</v>
+        <v>13.9725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2275</v>
+        <v>-0.1675</v>
       </c>
       <c r="N8" t="n">
-        <v>7.629999999999999</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.7062499999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.4275</v>
+        <v>-3.427500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.5825</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.086249999999999</v>
+        <v>-1.08625</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>435</v>
+      </c>
+      <c r="D75" t="n">
+        <v>331</v>
+      </c>
+      <c r="E75" t="n">
+        <v>104</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>63</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>63</v>
+      </c>
+      <c r="K75" t="n">
+        <v>50</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7062499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.63375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2238193018480492</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.387755102040816</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07922136713444994</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
